--- a/data/trans_dic/IP31KM11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,19; 99,45</t>
+          <t>93,84; 99,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,55; 99,2</t>
+          <t>93,59; 99,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,53; 98,77</t>
+          <t>95,16; 99,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>96,48; 99,47</t>
+          <t>95,93; 99,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,5; 99,16</t>
+          <t>96,42; 99,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,83; 99,04</t>
+          <t>96,69; 99,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93,31; 99,2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93,48; 99,36</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,77; 99,73</t>
+          <t>96,51; 99,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,06; 99,7</t>
+          <t>93,77; 98,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,42; 98,82</t>
+          <t>97,19; 99,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,6; 99,05</t>
+          <t>96,29; 98,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>98,12; 99,49</t>
+          <t>96,41; 98,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,87; 98,27</t>
+          <t>97,92; 99,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,37; 98,66</t>
+          <t>97,41; 98,74</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>111982</t>
+          <t>119991</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>128960</t>
+          <t>116074</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240942</t>
+          <t>236065</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107616; 113620</t>
+          <t>115320; 122027</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104734; 135727</t>
+          <t>110999; 117927</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219749; 247969</t>
+          <t>229816; 239516</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>264</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>183235</t>
+          <t>226832</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>242652</t>
+          <t>177669</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425887</t>
+          <t>404500</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>179556; 185123</t>
+          <t>221835; 229408</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>236379; 245450</t>
+          <t>174129; 179585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419874; 429470</t>
+          <t>398214; 407718</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>223</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>188249</t>
+          <t>162183</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>178754</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367004</t>
+          <t>317221</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>155373; 165192</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>171146; 181921</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>359351; 370333</t>
+          <t>310350; 320562</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>232</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>162794</t>
+          <t>161079</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>172479</t>
+          <t>162296</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335273</t>
+          <t>323375</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>159675; 164023</t>
+          <t>155809; 163730</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167410; 175215</t>
+          <t>159372; 163525</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>330214; 338591</t>
+          <t>317900; 326798</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>904</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>646262</t>
+          <t>670086</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>611077</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1369107</t>
+          <t>1281162</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>640876; 649796</t>
+          <t>662166; 676812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>699061; 731853</t>
+          <t>605353; 614642</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1347114; 1379103</t>
+          <t>1271295; 1288578</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM11_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que utiliza aceite de oliva en casa (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>93,84; 99,29</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>93,59; 99,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95,16; 99,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>95,93; 99,21</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>96,42; 99,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>96,69; 99,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>93,31; 99,2</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>96,51; 99,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>93,77; 98,53</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97,19; 99,72</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>96,29; 98,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>96,41; 98,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>97,92; 99,42</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97,41; 98,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9763645285417595</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9787167203489282</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9775196895892201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>119991</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>116074</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>236065</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.9383510150708662</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9359296995190792</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9516445764170618</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>115320; 122027</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>110999; 117927</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>229816; 239516</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9929269663102469</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9943429678437755</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9918080537560169</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9809347340634017</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.983807502932745</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9821944703458564</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>226832</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>177669</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>404500</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9593245468610671</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9642069366623315</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9669310462379719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>221835; 229408</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>174129; 179585</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>398214; 407718</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9920737795896291</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9944203523339759</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9900083371670643</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,47 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.973945700101455</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9865076214662817</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>162183</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>155038</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>317221</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9330507025597962</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>0.9651398532780322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>155373; 165192</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>310350; 320562</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.992015006512207</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9968968892095218</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9693916715151464</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9897371558505348</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9794970571298036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>161079</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>162296</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>323375</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.937678746528946</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9719033922250929</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9629146254101557</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>155809; 163730</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159372; 163525</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>317900; 326798</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9853458306046018</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9972329342883605</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9898647227520861</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +768,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>904</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9756298204601374</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9884645771174484</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9817097855636827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>670086</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>611077</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1281162</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.9640991007794146</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9792056051391452</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9741489599954426</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>662166; 676812</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>605353; 614642</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1271295; 1288578</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9854231660315677</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9942319274307645</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9873928727441982</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +833,445 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que utiliza aceite de oliva en casa (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>119991</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>116074</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>236065</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>115320</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>110999</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>229816</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>122027</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>117927</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>239516</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>264</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>226832</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>177669</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>404500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>221835</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>174129</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>398214</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>229408</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>179585</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>407718</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>162183</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>155038</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>317221</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>155373</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>310350</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>165192</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>320562</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>161079</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>162296</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>323375</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>155809</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>159372</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>317900</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>163730</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>163525</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>326798</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>918</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>904</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>670086</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>611077</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1281162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>662166</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>605353</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1271295</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>676812</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>614642</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1288578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>